--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-observation.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$101</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3851" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3889" uniqueCount="689">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-10T06:36:19+00:00</t>
+    <t>2026-08-28T11:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -783,6 +783,22 @@
   </si>
   <si>
     <t>Reference to related Observation.</t>
+  </si>
+  <si>
+    <t>Observation.extension:structuredinfo</t>
+  </si>
+  <si>
+    <t>structuredinfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://nhn.no/fhir/nilar/StructureDefinition/nilar-structured-info}
+</t>
+  </si>
+  <si>
+    <t>Structured Info</t>
+  </si>
+  <si>
+    <t>Used on Observation to convey additional information.</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -2467,7 +2483,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP100"/>
+  <dimension ref="A1:AP101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.6796875" customWidth="true" bestFit="true"/>
@@ -5756,11 +5772,13 @@
         <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5773,26 +5791,22 @@
         <v>19</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>112</v>
+        <v>247</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>19</v>
       </c>
@@ -5840,7 +5854,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>193</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5849,7 +5863,7 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>19</v>
+        <v>199</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>120</v>
@@ -5864,7 +5878,7 @@
         <v>19</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>19</v>
@@ -5882,7 +5896,7 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5895,23 +5909,25 @@
         <v>19</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O29" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5960,7 +5976,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5972,22 +5988,22 @@
         <v>19</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>255</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>256</v>
+        <v>19</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>257</v>
+        <v>189</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>258</v>
+        <v>19</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>19</v>
@@ -5995,10 +6011,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6009,7 +6025,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>19</v>
@@ -6018,19 +6034,21 @@
         <v>19</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>105</v>
+        <v>256</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>106</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
       </c>
@@ -6078,34 +6096,34 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>108</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>19</v>
+        <v>261</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>109</v>
+        <v>262</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>19</v>
+        <v>263</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>19</v>
@@ -6113,21 +6131,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>19</v>
@@ -6139,17 +6157,15 @@
         <v>19</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -6186,31 +6202,31 @@
         <v>19</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>19</v>
@@ -6233,46 +6249,44 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>262</v>
+        <v>113</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>19</v>
       </c>
@@ -6296,43 +6310,43 @@
         <v>19</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>266</v>
+        <v>19</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>267</v>
+        <v>19</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>119</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>19</v>
@@ -6341,10 +6355,10 @@
         <v>19</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>269</v>
+        <v>109</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>19</v>
@@ -6355,10 +6369,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6375,25 +6389,25 @@
         <v>19</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>271</v>
+        <v>166</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -6418,13 +6432,13 @@
         <v>19</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>19</v>
@@ -6442,7 +6456,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6463,10 +6477,10 @@
         <v>19</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>279</v>
+        <v>189</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>19</v>
@@ -6477,10 +6491,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6494,7 +6508,7 @@
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>19</v>
@@ -6503,19 +6517,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>133</v>
+        <v>276</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -6528,7 +6542,7 @@
         <v>19</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>19</v>
@@ -6540,11 +6554,13 @@
         <v>19</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>19</v>
@@ -6562,7 +6578,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6583,10 +6599,10 @@
         <v>19</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>19</v>
@@ -6595,12 +6611,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6623,18 +6639,20 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
       </c>
@@ -6646,7 +6664,7 @@
         <v>19</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>19</v>
@@ -6658,13 +6676,11 @@
         <v>19</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>19</v>
+        <v>291</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>19</v>
@@ -6682,7 +6698,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6703,10 +6719,10 @@
         <v>19</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>19</v>
@@ -6715,12 +6731,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6734,7 +6750,7 @@
         <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>19</v>
@@ -6743,15 +6759,17 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6764,7 +6782,7 @@
         <v>19</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>19</v>
+        <v>299</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>19</v>
@@ -6800,7 +6818,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6821,10 +6839,10 @@
         <v>19</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>19</v>
@@ -6835,10 +6853,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6861,17 +6879,15 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L37" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>309</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6920,7 +6936,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6941,10 +6957,10 @@
         <v>19</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>19</v>
@@ -6955,14 +6971,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>314</v>
+        <v>19</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6981,18 +6997,18 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>19</v>
       </c>
@@ -7040,13 +7056,13 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>19</v>
@@ -7055,16 +7071,16 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>19</v>
@@ -7075,21 +7091,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>19</v>
@@ -7101,18 +7117,18 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>19</v>
       </c>
@@ -7160,7 +7176,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7175,16 +7191,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>19</v>
@@ -7195,46 +7211,44 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>19</v>
+        <v>328</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>166</v>
+        <v>329</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>335</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>19</v>
       </c>
@@ -7258,13 +7272,13 @@
         <v>19</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>336</v>
+        <v>19</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>337</v>
+        <v>19</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>19</v>
@@ -7282,13 +7296,13 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>19</v>
@@ -7297,19 +7311,19 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>339</v>
+        <v>19</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>342</v>
+        <v>19</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>19</v>
@@ -7317,10 +7331,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7328,7 +7342,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>91</v>
@@ -7337,25 +7351,25 @@
         <v>19</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>271</v>
+        <v>166</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -7382,9 +7396,11 @@
       <c r="X41" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y41" s="2"/>
+      <c r="Y41" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>19</v>
@@ -7402,13 +7418,13 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>19</v>
@@ -7417,19 +7433,19 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>19</v>
+        <v>343</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>19</v>
+        <v>344</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>19</v>
+        <v>345</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>19</v>
@@ -7437,18 +7453,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>352</v>
+        <v>19</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>91</v>
@@ -7460,22 +7476,22 @@
         <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -7504,7 +7520,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>19</v>
@@ -7522,13 +7538,13 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>19</v>
@@ -7537,44 +7553,44 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>359</v>
+        <v>19</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>363</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>19</v>
+        <v>357</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>19</v>
@@ -7583,19 +7599,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -7620,13 +7636,11 @@
         <v>19</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>19</v>
@@ -7644,10 +7658,10 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>91</v>
@@ -7659,30 +7673,30 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>19</v>
+        <v>364</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>19</v>
+        <v>368</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7696,25 +7710,29 @@
         <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>105</v>
+        <v>370</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>106</v>
+        <v>371</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
       </c>
@@ -7762,7 +7780,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>108</v>
+        <v>369</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7774,22 +7792,22 @@
         <v>19</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>19</v>
+        <v>375</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>19</v>
+        <v>376</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>109</v>
+        <v>377</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>19</v>
+        <v>378</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>19</v>
@@ -7797,21 +7815,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>19</v>
@@ -7823,17 +7841,15 @@
         <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7870,31 +7886,31 @@
         <v>19</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>19</v>
@@ -7917,21 +7933,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>19</v>
@@ -7940,19 +7956,19 @@
         <v>19</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>377</v>
+        <v>113</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>378</v>
+        <v>114</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>379</v>
+        <v>115</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7990,31 +8006,31 @@
         <v>19</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>119</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>381</v>
+        <v>19</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>19</v>
@@ -8026,7 +8042,7 @@
         <v>19</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>19</v>
@@ -8037,10 +8053,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8063,16 +8079,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8098,13 +8114,13 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>386</v>
+        <v>19</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>387</v>
+        <v>19</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>19</v>
@@ -8122,7 +8138,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8131,7 +8147,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>19</v>
+        <v>386</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8157,10 +8173,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8174,7 +8190,7 @@
         <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>19</v>
@@ -8183,16 +8199,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>251</v>
+        <v>133</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8218,13 +8234,13 @@
         <v>19</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>19</v>
+        <v>391</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>19</v>
+        <v>392</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>19</v>
@@ -8266,21 +8282,21 @@
         <v>19</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AO48" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" hidden="true">
-      <c r="A49" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="B49" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8294,24 +8310,26 @@
         <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>105</v>
+        <v>256</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>106</v>
+        <v>395</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -8360,7 +8378,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>108</v>
+        <v>398</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8372,7 +8390,7 @@
         <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>19</v>
@@ -8384,7 +8402,7 @@
         <v>19</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>109</v>
+        <v>399</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>19</v>
@@ -8395,21 +8413,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>19</v>
@@ -8421,17 +8439,15 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -8468,31 +8484,31 @@
         <v>19</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>19</v>
@@ -8515,46 +8531,44 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>262</v>
+        <v>113</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>19</v>
       </c>
@@ -8578,43 +8592,43 @@
         <v>19</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>266</v>
+        <v>19</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>267</v>
+        <v>19</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>268</v>
+        <v>119</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
@@ -8623,10 +8637,10 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>269</v>
+        <v>109</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>19</v>
@@ -8637,10 +8651,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8657,25 +8671,25 @@
         <v>19</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>271</v>
+        <v>166</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -8700,13 +8714,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -8724,7 +8738,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8745,10 +8759,10 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>279</v>
+        <v>189</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>19</v>
@@ -8759,10 +8773,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8776,7 +8790,7 @@
         <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>19</v>
@@ -8785,19 +8799,19 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>133</v>
+        <v>276</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -8810,7 +8824,7 @@
         <v>19</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>19</v>
@@ -8822,11 +8836,13 @@
         <v>19</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>400</v>
+        <v>282</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>19</v>
@@ -8844,7 +8860,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8865,10 +8881,10 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>19</v>
@@ -8877,12 +8893,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8905,18 +8921,20 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>19</v>
       </c>
@@ -8928,7 +8946,7 @@
         <v>19</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>19</v>
@@ -8940,13 +8958,11 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>19</v>
@@ -8964,7 +8980,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8985,10 +9001,10 @@
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>19</v>
@@ -8997,12 +9013,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9016,7 +9032,7 @@
         <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>19</v>
@@ -9025,15 +9041,17 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>19</v>
@@ -9046,7 +9064,7 @@
         <v>19</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>19</v>
+        <v>299</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>19</v>
@@ -9082,7 +9100,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9103,10 +9121,10 @@
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>19</v>
@@ -9117,10 +9135,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9143,17 +9161,15 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L56" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>309</v>
-      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>19</v>
@@ -9202,7 +9218,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -9223,10 +9239,10 @@
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>19</v>
@@ -9237,10 +9253,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9254,7 +9270,7 @@
         <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>19</v>
@@ -9263,16 +9279,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>105</v>
+        <v>311</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>405</v>
+        <v>312</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>406</v>
+        <v>313</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>407</v>
+        <v>314</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9322,7 +9338,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>408</v>
+        <v>315</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9343,10 +9359,10 @@
         <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>19</v>
+        <v>316</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>189</v>
+        <v>317</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>19</v>
@@ -9355,7 +9371,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>409</v>
       </c>
@@ -9371,10 +9387,10 @@
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>19</v>
@@ -9383,16 +9399,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9442,13 +9458,13 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>19</v>
@@ -9463,13 +9479,13 @@
         <v>19</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>414</v>
+        <v>189</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>373</v>
+        <v>19</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>19</v>
@@ -9477,21 +9493,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>416</v>
+        <v>19</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>19</v>
@@ -9503,20 +9519,18 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>421</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>19</v>
       </c>
@@ -9564,13 +9578,13 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>19</v>
@@ -9579,19 +9593,19 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>422</v>
+        <v>19</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>423</v>
+        <v>365</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>425</v>
+        <v>378</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>19</v>
@@ -9599,14 +9613,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9625,19 +9639,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
@@ -9686,7 +9700,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9701,19 +9715,19 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>19</v>
@@ -9721,14 +9735,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>19</v>
+        <v>432</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9747,18 +9761,20 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>127</v>
+        <v>433</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>19</v>
       </c>
@@ -9806,7 +9822,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9821,19 +9837,19 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>19</v>
+        <v>438</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>19</v>
@@ -9841,10 +9857,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9855,7 +9871,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>19</v>
@@ -9867,18 +9883,18 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L62" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>448</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>19</v>
       </c>
@@ -9926,13 +9942,13 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>19</v>
@@ -9941,19 +9957,19 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>449</v>
+        <v>19</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>19</v>
@@ -9961,10 +9977,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9975,7 +9991,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>19</v>
@@ -9987,19 +10003,17 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
@@ -10036,59 +10050,59 @@
         <v>19</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>460</v>
+        <v>19</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>19</v>
+        <v>454</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>461</v>
+        <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>19</v>
+        <v>457</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>464</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>19</v>
       </c>
@@ -10109,19 +10123,19 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>271</v>
+        <v>459</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>19</v>
@@ -10146,29 +10160,29 @@
         <v>19</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>467</v>
+        <v>19</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10177,7 +10191,7 @@
         <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>103</v>
@@ -10186,30 +10200,30 @@
         <v>19</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>19</v>
@@ -10231,19 +10245,19 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>470</v>
+        <v>276</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -10268,13 +10282,11 @@
         <v>19</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>19</v>
+        <v>472</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>19</v>
@@ -10292,7 +10304,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10301,7 +10313,7 @@
         <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>103</v>
@@ -10310,29 +10322,31 @@
         <v>19</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>19</v>
       </c>
@@ -10350,19 +10364,23 @@
         <v>19</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>105</v>
+        <v>475</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>106</v>
+        <v>460</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>19</v>
       </c>
@@ -10410,7 +10428,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>108</v>
+        <v>458</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10419,47 +10437,47 @@
         <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>19</v>
+        <v>465</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>19</v>
+        <v>466</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>19</v>
+        <v>467</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>109</v>
+        <v>468</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>19</v>
+        <v>469</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>19</v>
@@ -10471,17 +10489,15 @@
         <v>19</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>19</v>
@@ -10518,31 +10534,31 @@
         <v>19</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>19</v>
@@ -10565,21 +10581,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
@@ -10588,23 +10604,21 @@
         <v>19</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>477</v>
+        <v>112</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>478</v>
+        <v>113</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>479</v>
+        <v>114</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>19</v>
       </c>
@@ -10640,31 +10654,31 @@
         <v>19</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>482</v>
+        <v>119</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>19</v>
@@ -10673,10 +10687,10 @@
         <v>19</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>483</v>
+        <v>19</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>484</v>
+        <v>109</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>19</v>
@@ -10687,10 +10701,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10707,74 +10721,74 @@
         <v>19</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>166</v>
+        <v>482</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q69" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="R69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10795,10 +10809,10 @@
         <v>19</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>19</v>
@@ -10809,10 +10823,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10829,28 +10843,30 @@
         <v>19</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="Q70" s="2"/>
+      <c r="Q70" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="R70" t="s" s="2">
         <v>19</v>
       </c>
@@ -10870,13 +10886,13 @@
         <v>19</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>19</v>
+        <v>496</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>19</v>
+        <v>497</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>19</v>
@@ -10894,7 +10910,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10915,10 +10931,10 @@
         <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>19</v>
@@ -10929,10 +10945,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10955,17 +10971,17 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -11014,7 +11030,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11023,7 +11039,7 @@
         <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>510</v>
+        <v>19</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>103</v>
@@ -11035,10 +11051,10 @@
         <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>19</v>
@@ -11049,10 +11065,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11075,19 +11091,17 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -11112,11 +11126,13 @@
         <v>19</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>19</v>
@@ -11134,7 +11150,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11143,7 +11159,7 @@
         <v>91</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>19</v>
+        <v>515</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>103</v>
@@ -11155,10 +11171,10 @@
         <v>19</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>19</v>
@@ -11169,10 +11185,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11192,22 +11208,22 @@
         <v>19</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>271</v>
+        <v>166</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O73" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>19</v>
@@ -11232,13 +11248,11 @@
         <v>19</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>19</v>
@@ -11256,7 +11270,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11265,7 +11279,7 @@
         <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>528</v>
+        <v>19</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>103</v>
@@ -11277,10 +11291,10 @@
         <v>19</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>189</v>
+        <v>507</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>19</v>
@@ -11291,14 +11305,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>531</v>
+        <v>19</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11317,19 +11331,19 @@
         <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>19</v>
@@ -11354,11 +11368,13 @@
         <v>19</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>19</v>
@@ -11376,16 +11392,16 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>19</v>
+        <v>533</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>103</v>
@@ -11394,38 +11410,38 @@
         <v>19</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>537</v>
+        <v>19</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>538</v>
+        <v>189</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>540</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>19</v>
+        <v>536</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>19</v>
@@ -11437,19 +11453,19 @@
         <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>542</v>
+        <v>276</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>19</v>
@@ -11474,13 +11490,11 @@
         <v>19</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>19</v>
+        <v>541</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>19</v>
@@ -11498,7 +11512,7 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11516,27 +11530,27 @@
         <v>19</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>19</v>
+        <v>542</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>19</v>
+        <v>545</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11547,7 +11561,7 @@
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>19</v>
@@ -11559,18 +11573,20 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>271</v>
+        <v>547</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="N76" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>19</v>
       </c>
@@ -11594,13 +11610,13 @@
         <v>19</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>553</v>
+        <v>19</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>554</v>
+        <v>19</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>555</v>
+        <v>19</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>19</v>
@@ -11618,13 +11634,13 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>19</v>
@@ -11636,27 +11652,27 @@
         <v>19</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>556</v>
+        <v>19</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>559</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11679,20 +11695,18 @@
         <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>19</v>
       </c>
@@ -11716,11 +11730,13 @@
         <v>19</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>559</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>19</v>
@@ -11738,7 +11754,7 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11756,27 +11772,27 @@
         <v>19</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>19</v>
+        <v>561</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>19</v>
+        <v>564</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11799,18 +11815,20 @@
         <v>19</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L78" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>19</v>
       </c>
@@ -11834,13 +11852,11 @@
         <v>19</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>19</v>
+        <v>570</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>19</v>
@@ -11858,7 +11874,7 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11876,27 +11892,27 @@
         <v>19</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>573</v>
+        <v>19</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>576</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11919,16 +11935,16 @@
         <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11978,7 +11994,7 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11996,27 +12012,27 @@
         <v>19</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12027,7 +12043,7 @@
         <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>19</v>
@@ -12039,20 +12055,18 @@
         <v>19</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>591</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>19</v>
       </c>
@@ -12100,45 +12114,45 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>592</v>
+        <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>19</v>
+        <v>587</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>19</v>
+        <v>590</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12149,7 +12163,7 @@
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>19</v>
@@ -12161,16 +12175,20 @@
         <v>19</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>105</v>
+        <v>592</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>106</v>
+        <v>593</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>596</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>19</v>
       </c>
@@ -12218,19 +12236,19 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>108</v>
+        <v>591</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>19</v>
+        <v>597</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>19</v>
@@ -12239,10 +12257,10 @@
         <v>19</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>19</v>
+        <v>598</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>109</v>
+        <v>599</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>19</v>
@@ -12253,21 +12271,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>19</v>
@@ -12279,17 +12297,15 @@
         <v>19</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>19</v>
@@ -12338,19 +12354,19 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>19</v>
@@ -12373,14 +12389,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>598</v>
+        <v>111</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12393,26 +12409,24 @@
         <v>19</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>599</v>
+        <v>113</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>600</v>
+        <v>114</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O83" t="s" s="2">
-        <v>248</v>
-      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>19</v>
       </c>
@@ -12460,7 +12474,7 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>601</v>
+        <v>119</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12484,7 +12498,7 @@
         <v>19</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>19</v>
@@ -12502,26 +12516,26 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>19</v>
+        <v>603</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>603</v>
+        <v>112</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>604</v>
@@ -12529,8 +12543,12 @@
       <c r="M84" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+      <c r="N84" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>19</v>
       </c>
@@ -12578,19 +12596,19 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>606</v>
+        <v>19</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>19</v>
@@ -12599,10 +12617,10 @@
         <v>19</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>607</v>
+        <v>19</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>608</v>
+        <v>189</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>19</v>
@@ -12613,10 +12631,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12639,13 +12657,13 @@
         <v>19</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12696,7 +12714,7 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12705,7 +12723,7 @@
         <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -12717,10 +12735,10 @@
         <v>19</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>19</v>
@@ -12731,10 +12749,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12757,20 +12775,16 @@
         <v>19</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>271</v>
+        <v>608</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N86" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="O86" t="s" s="2">
-        <v>617</v>
-      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>19</v>
       </c>
@@ -12794,13 +12808,13 @@
         <v>19</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>618</v>
+        <v>19</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>619</v>
+        <v>19</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>19</v>
@@ -12818,7 +12832,7 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12827,7 +12841,7 @@
         <v>91</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>19</v>
+        <v>611</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>103</v>
@@ -12836,13 +12850,13 @@
         <v>19</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>620</v>
+        <v>19</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>539</v>
+        <v>617</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>19</v>
@@ -12853,10 +12867,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12867,7 +12881,7 @@
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>19</v>
@@ -12879,19 +12893,19 @@
         <v>19</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>19</v>
@@ -12916,13 +12930,13 @@
         <v>19</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>553</v>
+        <v>170</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>19</v>
@@ -12940,13 +12954,13 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>19</v>
@@ -12958,13 +12972,13 @@
         <v>19</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>19</v>
@@ -12975,10 +12989,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12989,7 +13003,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>19</v>
@@ -13001,17 +13015,19 @@
         <v>19</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>19</v>
@@ -13036,13 +13052,13 @@
         <v>19</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>19</v>
+        <v>558</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>19</v>
+        <v>632</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>19</v>
+        <v>633</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>19</v>
@@ -13060,13 +13076,13 @@
         <v>19</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>19</v>
@@ -13078,13 +13094,13 @@
         <v>19</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>19</v>
+        <v>625</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>19</v>
+        <v>626</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>634</v>
+        <v>544</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>19</v>
@@ -13095,10 +13111,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13121,7 +13137,7 @@
         <v>19</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>105</v>
+        <v>635</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>636</v>
@@ -13130,7 +13146,9 @@
         <v>637</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>638</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>19</v>
       </c>
@@ -13178,7 +13196,7 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13199,10 +13217,10 @@
         <v>19</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>607</v>
+        <v>19</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>19</v>
@@ -13213,10 +13231,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13227,7 +13245,7 @@
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>19</v>
@@ -13236,10 +13254,10 @@
         <v>19</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>640</v>
+        <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>641</v>
@@ -13247,9 +13265,7 @@
       <c r="M90" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="N90" t="s" s="2">
-        <v>643</v>
-      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>19</v>
@@ -13298,13 +13314,13 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>19</v>
@@ -13319,10 +13335,10 @@
         <v>19</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>644</v>
+        <v>612</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>19</v>
@@ -13333,10 +13349,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13359,16 +13375,16 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13418,7 +13434,7 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13439,10 +13455,10 @@
         <v>19</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>19</v>
@@ -13453,10 +13469,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13479,7 +13495,7 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>587</v>
+        <v>652</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>653</v>
@@ -13490,9 +13506,7 @@
       <c r="N92" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="O92" t="s" s="2">
-        <v>656</v>
-      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>19</v>
       </c>
@@ -13540,7 +13554,7 @@
         <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13561,10 +13575,10 @@
         <v>19</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>19</v>
@@ -13575,10 +13589,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13589,7 +13603,7 @@
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>19</v>
@@ -13598,19 +13612,23 @@
         <v>19</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>105</v>
+        <v>592</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>106</v>
+        <v>658</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+        <v>659</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>661</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>19</v>
       </c>
@@ -13658,19 +13676,19 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>108</v>
+        <v>657</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>19</v>
@@ -13679,10 +13697,10 @@
         <v>19</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>19</v>
+        <v>662</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>109</v>
+        <v>663</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>19</v>
@@ -13693,21 +13711,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>19</v>
@@ -13719,17 +13737,15 @@
         <v>19</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>19</v>
@@ -13778,19 +13794,19 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>19</v>
@@ -13813,14 +13829,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>598</v>
+        <v>111</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13833,26 +13849,24 @@
         <v>19</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>599</v>
+        <v>113</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>600</v>
+        <v>114</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O95" t="s" s="2">
-        <v>248</v>
-      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>19</v>
       </c>
@@ -13900,7 +13914,7 @@
         <v>19</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>601</v>
+        <v>119</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13924,7 +13938,7 @@
         <v>19</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>19</v>
@@ -13935,45 +13949,45 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>19</v>
+        <v>603</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J96" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>271</v>
+        <v>112</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>663</v>
+        <v>604</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>664</v>
+        <v>605</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>665</v>
+        <v>115</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>356</v>
+        <v>253</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>19</v>
@@ -13998,13 +14012,13 @@
         <v>19</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>553</v>
+        <v>19</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>666</v>
+        <v>19</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>667</v>
+        <v>19</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>19</v>
@@ -14022,34 +14036,34 @@
         <v>19</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>662</v>
+        <v>606</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>668</v>
+        <v>19</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>361</v>
+        <v>189</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>19</v>
@@ -14057,10 +14071,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14068,7 +14082,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>91</v>
@@ -14083,19 +14097,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="L97" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>672</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>458</v>
+        <v>361</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>19</v>
@@ -14120,13 +14134,13 @@
         <v>19</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>19</v>
+        <v>558</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>19</v>
+        <v>671</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>19</v>
+        <v>672</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>19</v>
@@ -14144,10 +14158,10 @@
         <v>19</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>91</v>
@@ -14165,16 +14179,16 @@
         <v>673</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>462</v>
+        <v>365</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>463</v>
+        <v>366</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>19</v>
+        <v>367</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>464</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" hidden="true">
@@ -14202,22 +14216,22 @@
         <v>19</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>271</v>
+        <v>675</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>676</v>
+        <v>461</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>677</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>525</v>
+        <v>463</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>19</v>
@@ -14242,13 +14256,13 @@
         <v>19</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>526</v>
+        <v>19</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>527</v>
+        <v>19</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>19</v>
@@ -14275,7 +14289,7 @@
         <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>528</v>
+        <v>19</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>103</v>
@@ -14284,38 +14298,38 @@
         <v>19</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>19</v>
+        <v>678</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>189</v>
+        <v>467</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>529</v>
+        <v>468</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>19</v>
+        <v>469</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>531</v>
+        <v>19</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>19</v>
@@ -14327,19 +14341,19 @@
         <v>19</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>532</v>
+        <v>680</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>533</v>
+        <v>681</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>534</v>
+        <v>682</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>19</v>
@@ -14367,37 +14381,37 @@
         <v>149</v>
       </c>
       <c r="Y99" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="Z99" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>678</v>
-      </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>19</v>
+        <v>533</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>103</v>
@@ -14406,31 +14420,31 @@
         <v>19</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>537</v>
+        <v>19</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>538</v>
+        <v>189</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>540</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>19</v>
+        <v>536</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14449,19 +14463,19 @@
         <v>19</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>682</v>
+        <v>537</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>683</v>
+        <v>538</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>590</v>
+        <v>539</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>591</v>
+        <v>540</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>19</v>
@@ -14486,13 +14500,13 @@
         <v>19</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>19</v>
+        <v>684</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>19</v>
+        <v>685</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>19</v>
@@ -14510,7 +14524,7 @@
         <v>19</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14528,33 +14542,155 @@
         <v>19</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>19</v>
+        <v>542</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>593</v>
+        <v>543</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>594</v>
+        <v>544</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP100" t="s" s="2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP100">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AP101">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI99">
+  <conditionalFormatting sqref="A2:AI100">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-observation.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$100</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3889" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3851" uniqueCount="684">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:20:46+00:00</t>
+    <t>2026-08-28T12:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -783,22 +783,6 @@
   </si>
   <si>
     <t>Reference to related Observation.</t>
-  </si>
-  <si>
-    <t>Observation.extension:structuredinfo</t>
-  </si>
-  <si>
-    <t>structuredinfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://nhn.no/fhir/nilar/StructureDefinition/nilar-structured-info}
-</t>
-  </si>
-  <si>
-    <t>Structured Info</t>
-  </si>
-  <si>
-    <t>Used on Observation to convey additional information.</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -2483,7 +2467,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP101"/>
+  <dimension ref="A1:AP100"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.6796875" customWidth="true" bestFit="true"/>
@@ -5772,13 +5756,11 @@
         <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5791,22 +5773,26 @@
         <v>19</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O28" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>19</v>
       </c>
@@ -5854,7 +5840,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>193</v>
+        <v>249</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5863,7 +5849,7 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>120</v>
@@ -5878,7 +5864,7 @@
         <v>19</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>19</v>
@@ -5896,7 +5882,7 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5909,25 +5895,23 @@
         <v>19</v>
       </c>
       <c r="I29" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="J29" t="s" s="2">
-        <v>19</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>112</v>
+        <v>251</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5976,7 +5960,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5988,22 +5972,22 @@
         <v>19</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>19</v>
+        <v>255</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>19</v>
+        <v>256</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>19</v>
+        <v>258</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>19</v>
@@ -6011,10 +5995,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6025,7 +6009,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>19</v>
@@ -6034,21 +6018,19 @@
         <v>19</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>256</v>
+        <v>105</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>106</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>107</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>259</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>19</v>
       </c>
@@ -6096,34 +6078,34 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>260</v>
+        <v>19</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>261</v>
+        <v>19</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>262</v>
+        <v>109</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>263</v>
+        <v>19</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>19</v>
@@ -6131,21 +6113,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>19</v>
@@ -6157,15 +6139,17 @@
         <v>19</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -6202,31 +6186,31 @@
         <v>19</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>19</v>
@@ -6249,44 +6233,46 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>19</v>
       </c>
@@ -6310,43 +6296,43 @@
         <v>19</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>19</v>
+        <v>266</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>19</v>
+        <v>267</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>119</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>19</v>
@@ -6355,10 +6341,10 @@
         <v>19</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>109</v>
+        <v>269</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>19</v>
@@ -6369,10 +6355,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6389,25 +6375,25 @@
         <v>19</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -6432,13 +6418,13 @@
         <v>19</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>19</v>
@@ -6456,7 +6442,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6477,10 +6463,10 @@
         <v>19</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>19</v>
@@ -6489,12 +6475,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6508,7 +6494,7 @@
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>19</v>
@@ -6517,19 +6503,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>276</v>
+        <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -6542,7 +6528,7 @@
         <v>19</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>19</v>
@@ -6554,13 +6540,11 @@
         <v>19</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>19</v>
@@ -6578,7 +6562,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6599,10 +6583,10 @@
         <v>19</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>19</v>
@@ -6613,10 +6597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6639,20 +6623,18 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>19</v>
       </c>
@@ -6664,7 +6646,7 @@
         <v>19</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>19</v>
@@ -6676,11 +6658,13 @@
         <v>19</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>291</v>
+        <v>19</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>19</v>
@@ -6698,7 +6682,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6719,10 +6703,10 @@
         <v>19</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>19</v>
@@ -6731,12 +6715,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6750,7 +6734,7 @@
         <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>19</v>
@@ -6759,17 +6743,15 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6782,7 +6764,7 @@
         <v>19</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>299</v>
+        <v>19</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>19</v>
@@ -6818,7 +6800,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6839,10 +6821,10 @@
         <v>19</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>19</v>
@@ -6853,10 +6835,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6879,15 +6861,17 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6936,7 +6920,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6957,10 +6941,10 @@
         <v>19</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>19</v>
@@ -6971,14 +6955,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6997,18 +6981,18 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>19</v>
       </c>
@@ -7056,13 +7040,13 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>19</v>
@@ -7071,16 +7055,16 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>19</v>
@@ -7091,21 +7075,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>19</v>
@@ -7117,18 +7101,18 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>19</v>
       </c>
@@ -7176,7 +7160,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7191,16 +7175,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>19</v>
@@ -7211,44 +7195,46 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>328</v>
+        <v>19</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>329</v>
+        <v>166</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>19</v>
       </c>
@@ -7272,13 +7258,13 @@
         <v>19</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>19</v>
+        <v>336</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>19</v>
+        <v>337</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>19</v>
@@ -7296,13 +7282,13 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>19</v>
@@ -7311,19 +7297,19 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>19</v>
+        <v>339</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>19</v>
+        <v>342</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>19</v>
@@ -7331,10 +7317,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7342,7 +7328,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>91</v>
@@ -7351,25 +7337,25 @@
         <v>19</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -7396,11 +7382,9 @@
       <c r="X41" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y41" t="s" s="2">
-        <v>341</v>
-      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>19</v>
@@ -7418,13 +7402,13 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>19</v>
@@ -7433,19 +7417,19 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>343</v>
+        <v>19</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>344</v>
+        <v>19</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>345</v>
+        <v>19</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>19</v>
@@ -7453,18 +7437,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>19</v>
+        <v>352</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>91</v>
@@ -7476,22 +7460,22 @@
         <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -7520,7 +7504,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>19</v>
@@ -7538,13 +7522,13 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>19</v>
@@ -7553,44 +7537,44 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>19</v>
+        <v>358</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>19</v>
+        <v>359</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>357</v>
+        <v>19</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>19</v>
@@ -7599,19 +7583,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>276</v>
+        <v>365</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -7636,11 +7620,13 @@
         <v>19</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>19</v>
@@ -7658,10 +7644,10 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>91</v>
@@ -7673,30 +7659,30 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>368</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7710,29 +7696,25 @@
         <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>370</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>371</v>
+        <v>106</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>19</v>
       </c>
@@ -7780,7 +7762,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>369</v>
+        <v>108</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7792,22 +7774,22 @@
         <v>19</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>375</v>
+        <v>19</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>376</v>
+        <v>19</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>377</v>
+        <v>109</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>378</v>
+        <v>19</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>19</v>
@@ -7815,21 +7797,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>19</v>
@@ -7841,15 +7823,17 @@
         <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7886,31 +7870,31 @@
         <v>19</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>19</v>
@@ -7933,21 +7917,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>19</v>
@@ -7956,19 +7940,19 @@
         <v>19</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>113</v>
+        <v>377</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>114</v>
+        <v>378</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>115</v>
+        <v>379</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8006,31 +7990,31 @@
         <v>19</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>119</v>
+        <v>380</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>19</v>
+        <v>381</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>19</v>
@@ -8042,7 +8026,7 @@
         <v>19</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>19</v>
@@ -8053,10 +8037,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8079,16 +8063,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8114,13 +8098,13 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>19</v>
+        <v>386</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>19</v>
+        <v>387</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>19</v>
@@ -8138,7 +8122,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8147,7 +8131,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>386</v>
+        <v>19</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8171,12 +8155,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8190,7 +8174,7 @@
         <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>19</v>
@@ -8199,16 +8183,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>133</v>
+        <v>251</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8234,13 +8218,13 @@
         <v>19</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>391</v>
+        <v>19</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>392</v>
+        <v>19</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>19</v>
@@ -8282,7 +8266,7 @@
         <v>19</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>189</v>
+        <v>394</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>19</v>
@@ -8291,12 +8275,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8310,26 +8294,24 @@
         <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>256</v>
+        <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>395</v>
+        <v>106</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -8378,7 +8360,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>398</v>
+        <v>108</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8390,7 +8372,7 @@
         <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>19</v>
@@ -8402,7 +8384,7 @@
         <v>19</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>399</v>
+        <v>109</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>19</v>
@@ -8413,21 +8395,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>19</v>
@@ -8439,15 +8421,17 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -8484,31 +8468,31 @@
         <v>19</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>19</v>
@@ -8531,44 +8515,46 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
       </c>
@@ -8592,43 +8578,43 @@
         <v>19</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>19</v>
+        <v>266</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>19</v>
+        <v>267</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>119</v>
+        <v>268</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
@@ -8637,10 +8623,10 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>109</v>
+        <v>269</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>19</v>
@@ -8651,10 +8637,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8671,25 +8657,25 @@
         <v>19</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -8714,13 +8700,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -8738,7 +8724,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8759,10 +8745,10 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>19</v>
@@ -8771,12 +8757,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8790,7 +8776,7 @@
         <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>19</v>
@@ -8799,19 +8785,19 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>276</v>
+        <v>133</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -8824,7 +8810,7 @@
         <v>19</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>19</v>
@@ -8836,13 +8822,11 @@
         <v>19</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>282</v>
+        <v>400</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>19</v>
@@ -8860,7 +8844,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8881,10 +8865,10 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>19</v>
@@ -8895,10 +8879,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8921,20 +8905,18 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>19</v>
       </c>
@@ -8946,7 +8928,7 @@
         <v>19</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>19</v>
@@ -8958,11 +8940,13 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>405</v>
+        <v>19</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>19</v>
@@ -8980,7 +8964,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -9001,10 +8985,10 @@
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>19</v>
@@ -9013,12 +8997,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9032,7 +9016,7 @@
         <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>19</v>
@@ -9041,17 +9025,15 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>19</v>
@@ -9064,7 +9046,7 @@
         <v>19</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>299</v>
+        <v>19</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>19</v>
@@ -9100,7 +9082,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9121,10 +9103,10 @@
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>19</v>
@@ -9135,10 +9117,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9161,15 +9143,17 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>19</v>
@@ -9218,7 +9202,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -9239,10 +9223,10 @@
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>19</v>
@@ -9251,12 +9235,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9270,7 +9254,7 @@
         <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>19</v>
@@ -9279,16 +9263,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>311</v>
+        <v>105</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>312</v>
+        <v>405</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>313</v>
+        <v>406</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>314</v>
+        <v>407</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9338,7 +9322,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>315</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9359,10 +9343,10 @@
         <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>316</v>
+        <v>19</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>317</v>
+        <v>189</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>19</v>
@@ -9371,7 +9355,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>409</v>
       </c>
@@ -9387,10 +9371,10 @@
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>19</v>
@@ -9399,16 +9383,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>105</v>
+        <v>410</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9458,13 +9442,13 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>19</v>
@@ -9479,13 +9463,13 @@
         <v>19</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>189</v>
+        <v>414</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>19</v>
+        <v>373</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>19</v>
@@ -9493,21 +9477,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>19</v>
+        <v>416</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>19</v>
@@ -9519,18 +9503,20 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>19</v>
       </c>
@@ -9578,13 +9564,13 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>19</v>
@@ -9593,19 +9579,19 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>19</v>
+        <v>422</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>365</v>
+        <v>423</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>378</v>
+        <v>425</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>19</v>
@@ -9613,14 +9599,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9639,19 +9625,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
@@ -9700,7 +9686,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9715,19 +9701,19 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>19</v>
@@ -9735,14 +9721,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>432</v>
+        <v>19</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9761,20 +9747,18 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>433</v>
+        <v>127</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>19</v>
       </c>
@@ -9822,7 +9806,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9837,19 +9821,19 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>438</v>
+        <v>19</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>19</v>
@@ -9857,10 +9841,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9871,7 +9855,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>19</v>
@@ -9883,18 +9867,18 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>127</v>
+        <v>445</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>19</v>
       </c>
@@ -9942,13 +9926,13 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>19</v>
@@ -9957,19 +9941,19 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>19</v>
+        <v>449</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>19</v>
@@ -9977,10 +9961,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9991,7 +9975,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>19</v>
@@ -10003,17 +9987,19 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
@@ -10050,59 +10036,59 @@
         <v>19</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>19</v>
+        <v>460</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>454</v>
+        <v>19</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>457</v>
+        <v>19</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>19</v>
+        <v>464</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>19</v>
       </c>
@@ -10123,19 +10109,19 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>459</v>
+        <v>271</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>19</v>
@@ -10160,29 +10146,29 @@
         <v>19</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>19</v>
+        <v>467</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AC64" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10191,7 +10177,7 @@
         <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>103</v>
@@ -10200,30 +10186,30 @@
         <v>19</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>19</v>
@@ -10245,19 +10231,19 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>276</v>
+        <v>470</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -10282,11 +10268,13 @@
         <v>19</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>472</v>
+        <v>19</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>19</v>
@@ -10304,7 +10292,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10313,7 +10301,7 @@
         <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>103</v>
@@ -10322,31 +10310,29 @@
         <v>19</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>19</v>
       </c>
@@ -10364,23 +10350,19 @@
         <v>19</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>475</v>
+        <v>105</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>460</v>
+        <v>106</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>19</v>
       </c>
@@ -10428,7 +10410,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>458</v>
+        <v>108</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10437,47 +10419,47 @@
         <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>465</v>
+        <v>19</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>466</v>
+        <v>19</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>467</v>
+        <v>19</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>468</v>
+        <v>109</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>469</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>19</v>
@@ -10489,15 +10471,17 @@
         <v>19</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>19</v>
@@ -10534,31 +10518,31 @@
         <v>19</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>19</v>
@@ -10581,21 +10565,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
@@ -10604,21 +10588,23 @@
         <v>19</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>112</v>
+        <v>477</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>113</v>
+        <v>478</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>114</v>
+        <v>479</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
       </c>
@@ -10654,31 +10640,31 @@
         <v>19</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>119</v>
+        <v>482</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>19</v>
@@ -10687,10 +10673,10 @@
         <v>19</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>19</v>
+        <v>483</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>109</v>
+        <v>484</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>19</v>
@@ -10701,10 +10687,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10721,30 +10707,30 @@
         <v>19</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>482</v>
+        <v>166</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="Q69" s="2"/>
+      <c r="Q69" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="R69" t="s" s="2">
         <v>19</v>
       </c>
@@ -10764,13 +10750,13 @@
         <v>19</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>19</v>
+        <v>491</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>19</v>
+        <v>492</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>19</v>
@@ -10788,7 +10774,7 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10809,10 +10795,10 @@
         <v>19</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>19</v>
@@ -10823,10 +10809,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10843,30 +10829,28 @@
         <v>19</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="Q70" t="s" s="2">
-        <v>495</v>
-      </c>
+      <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
         <v>19</v>
       </c>
@@ -10886,13 +10870,13 @@
         <v>19</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>496</v>
+        <v>19</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>497</v>
+        <v>19</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>19</v>
@@ -10910,7 +10894,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10931,10 +10915,10 @@
         <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>19</v>
@@ -10945,10 +10929,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10971,17 +10955,17 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -11030,7 +11014,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11039,7 +11023,7 @@
         <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>19</v>
+        <v>510</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>103</v>
@@ -11051,10 +11035,10 @@
         <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>19</v>
@@ -11065,10 +11049,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11091,17 +11075,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -11126,13 +11112,11 @@
         <v>19</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>19</v>
+        <v>518</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>19</v>
@@ -11150,7 +11134,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11159,7 +11143,7 @@
         <v>91</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>515</v>
+        <v>19</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>103</v>
@@ -11171,10 +11155,10 @@
         <v>19</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>19</v>
@@ -11185,10 +11169,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11208,22 +11192,22 @@
         <v>19</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>19</v>
@@ -11248,11 +11232,13 @@
         <v>19</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>19</v>
@@ -11270,7 +11256,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11279,7 +11265,7 @@
         <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>19</v>
+        <v>528</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>103</v>
@@ -11291,10 +11277,10 @@
         <v>19</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>507</v>
+        <v>189</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>19</v>
@@ -11305,14 +11291,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>19</v>
+        <v>531</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11331,19 +11317,19 @@
         <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>19</v>
@@ -11368,13 +11354,11 @@
         <v>19</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>531</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>19</v>
@@ -11392,16 +11376,16 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>533</v>
+        <v>19</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>103</v>
@@ -11410,38 +11394,38 @@
         <v>19</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>19</v>
+        <v>537</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>189</v>
+        <v>538</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>19</v>
+        <v>540</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>536</v>
+        <v>19</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>19</v>
@@ -11453,19 +11437,19 @@
         <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>276</v>
+        <v>542</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>19</v>
@@ -11490,29 +11474,31 @@
         <v>19</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11530,27 +11516,27 @@
         <v>19</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>542</v>
+        <v>19</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>545</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11561,7 +11547,7 @@
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>19</v>
@@ -11573,20 +11559,18 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>547</v>
+        <v>271</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>19</v>
       </c>
@@ -11610,13 +11594,13 @@
         <v>19</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>19</v>
+        <v>553</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>19</v>
+        <v>554</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>19</v>
+        <v>555</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>19</v>
@@ -11634,13 +11618,13 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>19</v>
@@ -11652,27 +11636,27 @@
         <v>19</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>19</v>
+        <v>556</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>19</v>
+        <v>559</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11695,18 +11679,20 @@
         <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>564</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>19</v>
       </c>
@@ -11730,31 +11716,29 @@
         <v>19</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11772,27 +11756,27 @@
         <v>19</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>561</v>
+        <v>19</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>564</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11815,20 +11799,18 @@
         <v>19</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>276</v>
+        <v>569</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>569</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>19</v>
       </c>
@@ -11852,11 +11834,13 @@
         <v>19</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>570</v>
+        <v>19</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>19</v>
@@ -11874,7 +11858,7 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11892,27 +11876,27 @@
         <v>19</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>19</v>
+        <v>573</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>19</v>
+        <v>576</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11935,16 +11919,16 @@
         <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11994,7 +11978,7 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12012,27 +11996,27 @@
         <v>19</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12043,7 +12027,7 @@
         <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>19</v>
@@ -12055,18 +12039,20 @@
         <v>19</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>591</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>19</v>
       </c>
@@ -12114,45 +12100,45 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>103</v>
+        <v>592</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>587</v>
+        <v>19</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>590</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12163,7 +12149,7 @@
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>19</v>
@@ -12175,20 +12161,16 @@
         <v>19</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>592</v>
+        <v>105</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>593</v>
+        <v>106</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>596</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>19</v>
       </c>
@@ -12236,19 +12218,19 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>591</v>
+        <v>108</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>597</v>
+        <v>19</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>19</v>
@@ -12257,10 +12239,10 @@
         <v>19</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>598</v>
+        <v>19</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>599</v>
+        <v>109</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>19</v>
@@ -12271,21 +12253,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>19</v>
@@ -12297,15 +12279,17 @@
         <v>19</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>19</v>
@@ -12354,19 +12338,19 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>19</v>
@@ -12389,14 +12373,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>111</v>
+        <v>598</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12409,24 +12393,26 @@
         <v>19</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>113</v>
+        <v>599</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>114</v>
+        <v>600</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>19</v>
       </c>
@@ -12474,7 +12460,7 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>119</v>
+        <v>601</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12498,7 +12484,7 @@
         <v>19</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>19</v>
@@ -12516,26 +12502,26 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>603</v>
+        <v>19</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>112</v>
+        <v>603</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>604</v>
@@ -12543,12 +12529,8 @@
       <c r="M84" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="N84" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>19</v>
       </c>
@@ -12596,19 +12578,19 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI84" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="AG84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>19</v>
-      </c>
       <c r="AJ84" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>19</v>
@@ -12617,10 +12599,10 @@
         <v>19</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>19</v>
+        <v>607</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>189</v>
+        <v>608</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>19</v>
@@ -12631,10 +12613,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12657,13 +12639,13 @@
         <v>19</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12714,7 +12696,7 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12723,7 +12705,7 @@
         <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -12735,10 +12717,10 @@
         <v>19</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>19</v>
@@ -12749,10 +12731,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12775,16 +12757,20 @@
         <v>19</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>608</v>
+        <v>271</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>617</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>19</v>
       </c>
@@ -12808,13 +12794,13 @@
         <v>19</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>19</v>
+        <v>618</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>19</v>
+        <v>619</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>19</v>
@@ -12832,7 +12818,7 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12841,7 +12827,7 @@
         <v>91</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>611</v>
+        <v>19</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>103</v>
@@ -12850,13 +12836,13 @@
         <v>19</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>19</v>
+        <v>620</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>617</v>
+        <v>539</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>19</v>
@@ -12867,10 +12853,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12881,7 +12867,7 @@
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>19</v>
@@ -12893,19 +12879,19 @@
         <v>19</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>19</v>
@@ -12930,13 +12916,13 @@
         <v>19</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>170</v>
+        <v>553</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>19</v>
@@ -12954,13 +12940,13 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>19</v>
@@ -12972,13 +12958,13 @@
         <v>19</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>19</v>
@@ -12989,10 +12975,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13003,7 +12989,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>19</v>
@@ -13015,19 +13001,17 @@
         <v>19</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>276</v>
+        <v>630</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>630</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>19</v>
@@ -13052,13 +13036,13 @@
         <v>19</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>558</v>
+        <v>19</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>632</v>
+        <v>19</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>633</v>
+        <v>19</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>19</v>
@@ -13076,13 +13060,13 @@
         <v>19</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>19</v>
@@ -13094,13 +13078,13 @@
         <v>19</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>625</v>
+        <v>19</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>626</v>
+        <v>19</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>544</v>
+        <v>634</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>19</v>
@@ -13111,10 +13095,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13137,7 +13121,7 @@
         <v>19</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>635</v>
+        <v>105</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>636</v>
@@ -13146,9 +13130,7 @@
         <v>637</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>638</v>
-      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>19</v>
       </c>
@@ -13196,7 +13178,7 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13217,10 +13199,10 @@
         <v>19</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>19</v>
+        <v>607</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>19</v>
@@ -13231,10 +13213,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13245,7 +13227,7 @@
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>19</v>
@@ -13254,10 +13236,10 @@
         <v>19</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>105</v>
+        <v>640</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>641</v>
@@ -13265,7 +13247,9 @@
       <c r="M90" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="N90" s="2"/>
+      <c r="N90" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>19</v>
@@ -13314,13 +13298,13 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>19</v>
@@ -13335,10 +13319,10 @@
         <v>19</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>612</v>
+        <v>644</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>19</v>
@@ -13349,10 +13333,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13375,16 +13359,16 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13434,7 +13418,7 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13455,10 +13439,10 @@
         <v>19</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>19</v>
@@ -13469,10 +13453,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13495,7 +13479,7 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>652</v>
+        <v>587</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>653</v>
@@ -13506,7 +13490,9 @@
       <c r="N92" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="O92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>19</v>
       </c>
@@ -13554,7 +13540,7 @@
         <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13575,10 +13561,10 @@
         <v>19</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>19</v>
@@ -13589,10 +13575,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13603,7 +13589,7 @@
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>19</v>
@@ -13612,23 +13598,19 @@
         <v>19</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>592</v>
+        <v>105</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>658</v>
+        <v>106</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>661</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>19</v>
       </c>
@@ -13676,19 +13658,19 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>657</v>
+        <v>108</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>19</v>
@@ -13697,10 +13679,10 @@
         <v>19</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>662</v>
+        <v>19</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>663</v>
+        <v>109</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>19</v>
@@ -13711,21 +13693,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>19</v>
@@ -13737,15 +13719,17 @@
         <v>19</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>19</v>
@@ -13794,19 +13778,19 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>19</v>
@@ -13829,14 +13813,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>111</v>
+        <v>598</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13849,24 +13833,26 @@
         <v>19</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>113</v>
+        <v>599</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>114</v>
+        <v>600</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>19</v>
       </c>
@@ -13914,7 +13900,7 @@
         <v>19</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>119</v>
+        <v>601</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13938,7 +13924,7 @@
         <v>19</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>19</v>
@@ -13949,45 +13935,45 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>603</v>
+        <v>19</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J96" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>604</v>
+        <v>663</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>605</v>
+        <v>664</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>115</v>
+        <v>665</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>253</v>
+        <v>356</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>19</v>
@@ -14012,13 +13998,13 @@
         <v>19</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>19</v>
+        <v>553</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>19</v>
+        <v>666</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>19</v>
+        <v>667</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>19</v>
@@ -14036,34 +14022,34 @@
         <v>19</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>606</v>
+        <v>662</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>19</v>
+        <v>668</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>189</v>
+        <v>361</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>19</v>
@@ -14071,10 +14057,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14082,7 +14068,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>91</v>
@@ -14097,19 +14083,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>276</v>
+        <v>670</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>669</v>
+        <v>456</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>361</v>
+        <v>458</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>19</v>
@@ -14134,13 +14120,13 @@
         <v>19</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>558</v>
+        <v>19</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>671</v>
+        <v>19</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>672</v>
+        <v>19</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>19</v>
@@ -14158,10 +14144,10 @@
         <v>19</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>91</v>
@@ -14179,16 +14165,16 @@
         <v>673</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>366</v>
+        <v>463</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>367</v>
+        <v>19</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>19</v>
+        <v>464</v>
       </c>
     </row>
     <row r="98" hidden="true">
@@ -14216,22 +14202,22 @@
         <v>19</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>677</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>463</v>
+        <v>525</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>19</v>
@@ -14256,13 +14242,13 @@
         <v>19</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>19</v>
+        <v>526</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>19</v>
+        <v>527</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>19</v>
@@ -14289,7 +14275,7 @@
         <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>19</v>
+        <v>528</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>103</v>
@@ -14298,38 +14284,38 @@
         <v>19</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>678</v>
+        <v>19</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>467</v>
+        <v>189</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>468</v>
+        <v>529</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>469</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>19</v>
+        <v>531</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>19</v>
@@ -14341,19 +14327,19 @@
         <v>19</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>680</v>
+        <v>532</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>681</v>
+        <v>533</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>682</v>
+        <v>534</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>19</v>
@@ -14381,10 +14367,10 @@
         <v>149</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>531</v>
+        <v>679</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>532</v>
+        <v>680</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>19</v>
@@ -14402,16 +14388,16 @@
         <v>19</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>533</v>
+        <v>19</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>103</v>
@@ -14420,31 +14406,31 @@
         <v>19</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>19</v>
+        <v>537</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>189</v>
+        <v>538</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>19</v>
+        <v>540</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>536</v>
+        <v>19</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14463,19 +14449,19 @@
         <v>19</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>537</v>
+        <v>682</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>538</v>
+        <v>683</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>539</v>
+        <v>590</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>540</v>
+        <v>591</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>19</v>
@@ -14500,13 +14486,13 @@
         <v>19</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>684</v>
+        <v>19</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>685</v>
+        <v>19</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>19</v>
@@ -14524,7 +14510,7 @@
         <v>19</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14542,145 +14528,23 @@
         <v>19</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>542</v>
+        <v>19</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>543</v>
+        <v>593</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>544</v>
+        <v>594</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP101" t="s" s="2">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP101">
+  <autoFilter ref="A1:AP100">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14690,7 +14554,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI100">
+  <conditionalFormatting sqref="A2:AI99">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-observation.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$101</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3851" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3889" uniqueCount="689">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:05:03+00:00</t>
+    <t>2026-08-28T12:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -783,6 +783,22 @@
   </si>
   <si>
     <t>Reference to related Observation.</t>
+  </si>
+  <si>
+    <t>Observation.extension:structuredinfo</t>
+  </si>
+  <si>
+    <t>structuredinfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://nhn.no/fhir/nilar/StructureDefinition/nilar-structured-info}
+</t>
+  </si>
+  <si>
+    <t>Structured Info</t>
+  </si>
+  <si>
+    <t>Used on Observation to convey additional information.</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -2467,7 +2483,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP100"/>
+  <dimension ref="A1:AP101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.6796875" customWidth="true" bestFit="true"/>
@@ -5756,11 +5772,13 @@
         <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5773,26 +5791,22 @@
         <v>19</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>112</v>
+        <v>247</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>19</v>
       </c>
@@ -5840,7 +5854,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>193</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5849,7 +5863,7 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>19</v>
+        <v>199</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>120</v>
@@ -5864,7 +5878,7 @@
         <v>19</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>19</v>
@@ -5882,7 +5896,7 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5895,23 +5909,25 @@
         <v>19</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O29" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5960,7 +5976,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5972,22 +5988,22 @@
         <v>19</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>255</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>256</v>
+        <v>19</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>257</v>
+        <v>189</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>258</v>
+        <v>19</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>19</v>
@@ -5995,10 +6011,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6009,7 +6025,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>19</v>
@@ -6018,19 +6034,21 @@
         <v>19</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>105</v>
+        <v>256</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>106</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
       </c>
@@ -6078,34 +6096,34 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>108</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>19</v>
+        <v>261</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>109</v>
+        <v>262</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>19</v>
+        <v>263</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>19</v>
@@ -6113,21 +6131,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>19</v>
@@ -6139,17 +6157,15 @@
         <v>19</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -6186,31 +6202,31 @@
         <v>19</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>19</v>
@@ -6233,46 +6249,44 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>262</v>
+        <v>113</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>19</v>
       </c>
@@ -6296,43 +6310,43 @@
         <v>19</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>266</v>
+        <v>19</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>267</v>
+        <v>19</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>119</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>19</v>
@@ -6341,10 +6355,10 @@
         <v>19</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>269</v>
+        <v>109</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>19</v>
@@ -6355,10 +6369,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6375,25 +6389,25 @@
         <v>19</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>271</v>
+        <v>166</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -6418,13 +6432,13 @@
         <v>19</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>19</v>
@@ -6442,7 +6456,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6463,10 +6477,10 @@
         <v>19</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>279</v>
+        <v>189</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>19</v>
@@ -6475,12 +6489,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6494,7 +6508,7 @@
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>19</v>
@@ -6503,19 +6517,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>133</v>
+        <v>276</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -6528,7 +6542,7 @@
         <v>19</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>19</v>
@@ -6540,11 +6554,13 @@
         <v>19</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>19</v>
@@ -6562,7 +6578,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6583,10 +6599,10 @@
         <v>19</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>19</v>
@@ -6597,10 +6613,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6623,18 +6639,20 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
       </c>
@@ -6646,7 +6664,7 @@
         <v>19</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>19</v>
@@ -6658,13 +6676,11 @@
         <v>19</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>19</v>
+        <v>291</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>19</v>
@@ -6682,7 +6698,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6703,10 +6719,10 @@
         <v>19</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>19</v>
@@ -6715,12 +6731,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6734,7 +6750,7 @@
         <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>19</v>
@@ -6743,15 +6759,17 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6764,7 +6782,7 @@
         <v>19</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>19</v>
+        <v>299</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>19</v>
@@ -6800,7 +6818,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6821,10 +6839,10 @@
         <v>19</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>19</v>
@@ -6835,10 +6853,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6861,17 +6879,15 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L37" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>309</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6920,7 +6936,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6941,10 +6957,10 @@
         <v>19</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>19</v>
@@ -6955,14 +6971,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>314</v>
+        <v>19</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6981,18 +6997,18 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>19</v>
       </c>
@@ -7040,13 +7056,13 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>19</v>
@@ -7055,16 +7071,16 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>19</v>
@@ -7075,21 +7091,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>19</v>
@@ -7101,18 +7117,18 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>19</v>
       </c>
@@ -7160,7 +7176,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7175,16 +7191,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>19</v>
@@ -7195,46 +7211,44 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>19</v>
+        <v>328</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>166</v>
+        <v>329</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>335</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>19</v>
       </c>
@@ -7258,13 +7272,13 @@
         <v>19</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>336</v>
+        <v>19</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>337</v>
+        <v>19</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>19</v>
@@ -7282,13 +7296,13 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>19</v>
@@ -7297,19 +7311,19 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>339</v>
+        <v>19</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>342</v>
+        <v>19</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>19</v>
@@ -7317,10 +7331,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7328,7 +7342,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>91</v>
@@ -7337,25 +7351,25 @@
         <v>19</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>271</v>
+        <v>166</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -7382,9 +7396,11 @@
       <c r="X41" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y41" s="2"/>
+      <c r="Y41" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>19</v>
@@ -7402,13 +7418,13 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>19</v>
@@ -7417,19 +7433,19 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>19</v>
+        <v>343</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>19</v>
+        <v>344</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>19</v>
+        <v>345</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>19</v>
@@ -7437,18 +7453,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>352</v>
+        <v>19</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>91</v>
@@ -7460,22 +7476,22 @@
         <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -7504,7 +7520,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>19</v>
@@ -7522,13 +7538,13 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>19</v>
@@ -7537,44 +7553,44 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>359</v>
+        <v>19</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>363</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>19</v>
+        <v>357</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>19</v>
@@ -7583,19 +7599,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -7620,13 +7636,11 @@
         <v>19</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>19</v>
@@ -7644,10 +7658,10 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>91</v>
@@ -7659,30 +7673,30 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>19</v>
+        <v>364</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>19</v>
+        <v>368</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7696,25 +7710,29 @@
         <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>105</v>
+        <v>370</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>106</v>
+        <v>371</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
       </c>
@@ -7762,7 +7780,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>108</v>
+        <v>369</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7774,22 +7792,22 @@
         <v>19</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>19</v>
+        <v>375</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>19</v>
+        <v>376</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>109</v>
+        <v>377</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>19</v>
+        <v>378</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>19</v>
@@ -7797,21 +7815,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>19</v>
@@ -7823,17 +7841,15 @@
         <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7870,31 +7886,31 @@
         <v>19</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>19</v>
@@ -7917,21 +7933,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>19</v>
@@ -7940,19 +7956,19 @@
         <v>19</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>377</v>
+        <v>113</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>378</v>
+        <v>114</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>379</v>
+        <v>115</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7990,31 +8006,31 @@
         <v>19</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>119</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>381</v>
+        <v>19</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>19</v>
@@ -8026,7 +8042,7 @@
         <v>19</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>19</v>
@@ -8037,10 +8053,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8063,16 +8079,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8098,13 +8114,13 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>386</v>
+        <v>19</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>387</v>
+        <v>19</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>19</v>
@@ -8122,7 +8138,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8131,7 +8147,7 @@
         <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>19</v>
+        <v>386</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>103</v>
@@ -8155,12 +8171,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8174,7 +8190,7 @@
         <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>19</v>
@@ -8183,16 +8199,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>251</v>
+        <v>133</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8218,13 +8234,13 @@
         <v>19</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>19</v>
+        <v>391</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>19</v>
+        <v>392</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>19</v>
@@ -8266,21 +8282,21 @@
         <v>19</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AO48" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" hidden="true">
-      <c r="A49" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="B49" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8294,24 +8310,26 @@
         <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>105</v>
+        <v>256</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>106</v>
+        <v>395</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -8360,7 +8378,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>108</v>
+        <v>398</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8372,7 +8390,7 @@
         <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>19</v>
@@ -8384,7 +8402,7 @@
         <v>19</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>109</v>
+        <v>399</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>19</v>
@@ -8395,21 +8413,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>19</v>
@@ -8421,17 +8439,15 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -8468,31 +8484,31 @@
         <v>19</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>19</v>
@@ -8515,46 +8531,44 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>262</v>
+        <v>113</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>19</v>
       </c>
@@ -8578,43 +8592,43 @@
         <v>19</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>266</v>
+        <v>19</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>267</v>
+        <v>19</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>268</v>
+        <v>119</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
@@ -8623,10 +8637,10 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>269</v>
+        <v>109</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>19</v>
@@ -8637,10 +8651,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8657,25 +8671,25 @@
         <v>19</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>271</v>
+        <v>166</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -8700,13 +8714,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -8724,7 +8738,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8745,10 +8759,10 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>279</v>
+        <v>189</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>19</v>
@@ -8757,12 +8771,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8776,7 +8790,7 @@
         <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>19</v>
@@ -8785,19 +8799,19 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>133</v>
+        <v>276</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -8810,7 +8824,7 @@
         <v>19</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>19</v>
@@ -8822,11 +8836,13 @@
         <v>19</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>400</v>
+        <v>282</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>19</v>
@@ -8844,7 +8860,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8865,10 +8881,10 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>19</v>
@@ -8879,10 +8895,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8905,18 +8921,20 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>19</v>
       </c>
@@ -8928,7 +8946,7 @@
         <v>19</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>19</v>
@@ -8940,13 +8958,11 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>19</v>
@@ -8964,7 +8980,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8985,10 +9001,10 @@
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>19</v>
@@ -8997,12 +9013,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9016,7 +9032,7 @@
         <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>19</v>
@@ -9025,15 +9041,17 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>19</v>
@@ -9046,7 +9064,7 @@
         <v>19</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>19</v>
+        <v>299</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>19</v>
@@ -9082,7 +9100,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9103,10 +9121,10 @@
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>19</v>
@@ -9117,10 +9135,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9143,17 +9161,15 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L56" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>309</v>
-      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>19</v>
@@ -9202,7 +9218,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -9223,10 +9239,10 @@
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>19</v>
@@ -9235,12 +9251,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9254,7 +9270,7 @@
         <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>19</v>
@@ -9263,16 +9279,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>105</v>
+        <v>311</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>405</v>
+        <v>312</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>406</v>
+        <v>313</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>407</v>
+        <v>314</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9322,7 +9338,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>408</v>
+        <v>315</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9343,10 +9359,10 @@
         <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>19</v>
+        <v>316</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>189</v>
+        <v>317</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>19</v>
@@ -9355,7 +9371,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>409</v>
       </c>
@@ -9371,10 +9387,10 @@
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>19</v>
@@ -9383,16 +9399,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9442,13 +9458,13 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>19</v>
@@ -9463,13 +9479,13 @@
         <v>19</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>414</v>
+        <v>189</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>373</v>
+        <v>19</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>19</v>
@@ -9477,21 +9493,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>416</v>
+        <v>19</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>19</v>
@@ -9503,20 +9519,18 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>421</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>19</v>
       </c>
@@ -9564,13 +9578,13 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>19</v>
@@ -9579,19 +9593,19 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>422</v>
+        <v>19</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>423</v>
+        <v>365</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>425</v>
+        <v>378</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>19</v>
@@ -9599,14 +9613,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9625,19 +9639,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
@@ -9686,7 +9700,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9701,19 +9715,19 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>19</v>
@@ -9721,14 +9735,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>19</v>
+        <v>432</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9747,18 +9761,20 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>127</v>
+        <v>433</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>19</v>
       </c>
@@ -9806,7 +9822,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9821,19 +9837,19 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>19</v>
+        <v>438</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>19</v>
@@ -9841,10 +9857,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9855,7 +9871,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>19</v>
@@ -9867,18 +9883,18 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L62" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>448</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>19</v>
       </c>
@@ -9926,13 +9942,13 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>19</v>
@@ -9941,19 +9957,19 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>449</v>
+        <v>19</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>19</v>
@@ -9961,10 +9977,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9975,7 +9991,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>19</v>
@@ -9987,19 +10003,17 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
@@ -10036,59 +10050,59 @@
         <v>19</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>460</v>
+        <v>19</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>19</v>
+        <v>454</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>461</v>
+        <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>19</v>
+        <v>457</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>464</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>19</v>
       </c>
@@ -10109,19 +10123,19 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>271</v>
+        <v>459</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>19</v>
@@ -10146,29 +10160,29 @@
         <v>19</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>467</v>
+        <v>19</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10177,7 +10191,7 @@
         <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>103</v>
@@ -10186,30 +10200,30 @@
         <v>19</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>19</v>
@@ -10231,19 +10245,19 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>470</v>
+        <v>276</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -10268,13 +10282,11 @@
         <v>19</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>19</v>
+        <v>472</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>19</v>
@@ -10292,7 +10304,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10301,7 +10313,7 @@
         <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>103</v>
@@ -10310,29 +10322,31 @@
         <v>19</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>19</v>
       </c>
@@ -10350,19 +10364,23 @@
         <v>19</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>105</v>
+        <v>475</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>106</v>
+        <v>460</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>19</v>
       </c>
@@ -10410,7 +10428,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>108</v>
+        <v>458</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10419,47 +10437,47 @@
         <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>19</v>
+        <v>465</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>19</v>
+        <v>466</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>19</v>
+        <v>467</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>109</v>
+        <v>468</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>19</v>
+        <v>469</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>19</v>
@@ -10471,17 +10489,15 @@
         <v>19</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>19</v>
@@ -10518,31 +10534,31 @@
         <v>19</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>19</v>
@@ -10565,21 +10581,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
@@ -10588,23 +10604,21 @@
         <v>19</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>477</v>
+        <v>112</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>478</v>
+        <v>113</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>479</v>
+        <v>114</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>19</v>
       </c>
@@ -10640,31 +10654,31 @@
         <v>19</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>482</v>
+        <v>119</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>19</v>
@@ -10673,10 +10687,10 @@
         <v>19</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>483</v>
+        <v>19</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>484</v>
+        <v>109</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>19</v>
@@ -10687,10 +10701,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10707,74 +10721,74 @@
         <v>19</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>166</v>
+        <v>482</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q69" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="R69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10795,10 +10809,10 @@
         <v>19</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>19</v>
@@ -10809,10 +10823,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10829,28 +10843,30 @@
         <v>19</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="Q70" s="2"/>
+      <c r="Q70" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="R70" t="s" s="2">
         <v>19</v>
       </c>
@@ -10870,13 +10886,13 @@
         <v>19</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>19</v>
+        <v>496</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>19</v>
+        <v>497</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>19</v>
@@ -10894,7 +10910,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10915,10 +10931,10 @@
         <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>19</v>
@@ -10929,10 +10945,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10955,17 +10971,17 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -11014,7 +11030,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11023,7 +11039,7 @@
         <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>510</v>
+        <v>19</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>103</v>
@@ -11035,10 +11051,10 @@
         <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>19</v>
@@ -11049,10 +11065,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11075,19 +11091,17 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -11112,11 +11126,13 @@
         <v>19</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>518</v>
+        <v>19</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>19</v>
@@ -11134,7 +11150,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11143,7 +11159,7 @@
         <v>91</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>19</v>
+        <v>515</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>103</v>
@@ -11155,10 +11171,10 @@
         <v>19</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>19</v>
@@ -11169,10 +11185,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11192,22 +11208,22 @@
         <v>19</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>271</v>
+        <v>166</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O73" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>19</v>
@@ -11232,13 +11248,11 @@
         <v>19</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>19</v>
@@ -11256,7 +11270,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11265,7 +11279,7 @@
         <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>528</v>
+        <v>19</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>103</v>
@@ -11277,10 +11291,10 @@
         <v>19</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>189</v>
+        <v>507</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>19</v>
@@ -11291,14 +11305,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>531</v>
+        <v>19</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11317,19 +11331,19 @@
         <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>19</v>
@@ -11354,11 +11368,13 @@
         <v>19</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>19</v>
@@ -11376,16 +11392,16 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>19</v>
+        <v>533</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>103</v>
@@ -11394,38 +11410,38 @@
         <v>19</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>537</v>
+        <v>19</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>538</v>
+        <v>189</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>540</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>19</v>
+        <v>536</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>19</v>
@@ -11437,19 +11453,19 @@
         <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>542</v>
+        <v>276</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>19</v>
@@ -11474,13 +11490,11 @@
         <v>19</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>19</v>
+        <v>541</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>19</v>
@@ -11498,7 +11512,7 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11516,27 +11530,27 @@
         <v>19</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>19</v>
+        <v>542</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>19</v>
+        <v>545</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11547,7 +11561,7 @@
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>19</v>
@@ -11559,18 +11573,20 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>271</v>
+        <v>547</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="N76" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>19</v>
       </c>
@@ -11594,13 +11610,13 @@
         <v>19</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>553</v>
+        <v>19</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>554</v>
+        <v>19</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>555</v>
+        <v>19</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>19</v>
@@ -11618,13 +11634,13 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>19</v>
@@ -11636,27 +11652,27 @@
         <v>19</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>556</v>
+        <v>19</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>559</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11679,20 +11695,18 @@
         <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>19</v>
       </c>
@@ -11716,11 +11730,13 @@
         <v>19</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>559</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>19</v>
@@ -11738,7 +11754,7 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11756,27 +11772,27 @@
         <v>19</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>19</v>
+        <v>561</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>19</v>
+        <v>564</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11799,18 +11815,20 @@
         <v>19</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L78" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>19</v>
       </c>
@@ -11834,13 +11852,11 @@
         <v>19</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>19</v>
+        <v>570</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>19</v>
@@ -11858,7 +11874,7 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11876,27 +11892,27 @@
         <v>19</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>573</v>
+        <v>19</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>576</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11919,16 +11935,16 @@
         <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11978,7 +11994,7 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11996,27 +12012,27 @@
         <v>19</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12027,7 +12043,7 @@
         <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>19</v>
@@ -12039,20 +12055,18 @@
         <v>19</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>591</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>19</v>
       </c>
@@ -12100,45 +12114,45 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>592</v>
+        <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>19</v>
+        <v>587</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>19</v>
+        <v>590</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12149,7 +12163,7 @@
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>19</v>
@@ -12161,16 +12175,20 @@
         <v>19</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>105</v>
+        <v>592</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>106</v>
+        <v>593</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>596</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>19</v>
       </c>
@@ -12218,19 +12236,19 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>108</v>
+        <v>591</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>19</v>
+        <v>597</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>19</v>
@@ -12239,10 +12257,10 @@
         <v>19</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>19</v>
+        <v>598</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>109</v>
+        <v>599</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>19</v>
@@ -12253,21 +12271,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>19</v>
@@ -12279,17 +12297,15 @@
         <v>19</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>19</v>
@@ -12338,19 +12354,19 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>19</v>
@@ -12373,14 +12389,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>598</v>
+        <v>111</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12393,26 +12409,24 @@
         <v>19</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>599</v>
+        <v>113</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>600</v>
+        <v>114</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O83" t="s" s="2">
-        <v>248</v>
-      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>19</v>
       </c>
@@ -12460,7 +12474,7 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>601</v>
+        <v>119</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12484,7 +12498,7 @@
         <v>19</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>19</v>
@@ -12502,26 +12516,26 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>19</v>
+        <v>603</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>603</v>
+        <v>112</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>604</v>
@@ -12529,8 +12543,12 @@
       <c r="M84" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+      <c r="N84" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>19</v>
       </c>
@@ -12578,19 +12596,19 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>606</v>
+        <v>19</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>19</v>
@@ -12599,10 +12617,10 @@
         <v>19</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>607</v>
+        <v>19</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>608</v>
+        <v>189</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>19</v>
@@ -12613,10 +12631,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12639,13 +12657,13 @@
         <v>19</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12696,7 +12714,7 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12705,7 +12723,7 @@
         <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -12717,10 +12735,10 @@
         <v>19</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>19</v>
@@ -12731,10 +12749,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12757,20 +12775,16 @@
         <v>19</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>271</v>
+        <v>608</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N86" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="O86" t="s" s="2">
-        <v>617</v>
-      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>19</v>
       </c>
@@ -12794,13 +12808,13 @@
         <v>19</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>618</v>
+        <v>19</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>619</v>
+        <v>19</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>19</v>
@@ -12818,7 +12832,7 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12827,7 +12841,7 @@
         <v>91</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>19</v>
+        <v>611</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>103</v>
@@ -12836,13 +12850,13 @@
         <v>19</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>620</v>
+        <v>19</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>539</v>
+        <v>617</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>19</v>
@@ -12853,10 +12867,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12867,7 +12881,7 @@
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>19</v>
@@ -12879,19 +12893,19 @@
         <v>19</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>19</v>
@@ -12916,13 +12930,13 @@
         <v>19</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>553</v>
+        <v>170</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>19</v>
@@ -12940,13 +12954,13 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>19</v>
@@ -12958,13 +12972,13 @@
         <v>19</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>19</v>
@@ -12975,10 +12989,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12989,7 +13003,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>19</v>
@@ -13001,17 +13015,19 @@
         <v>19</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>19</v>
@@ -13036,13 +13052,13 @@
         <v>19</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>19</v>
+        <v>558</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>19</v>
+        <v>632</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>19</v>
+        <v>633</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>19</v>
@@ -13060,13 +13076,13 @@
         <v>19</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>19</v>
@@ -13078,13 +13094,13 @@
         <v>19</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>19</v>
+        <v>625</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>19</v>
+        <v>626</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>634</v>
+        <v>544</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>19</v>
@@ -13095,10 +13111,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13121,7 +13137,7 @@
         <v>19</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>105</v>
+        <v>635</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>636</v>
@@ -13130,7 +13146,9 @@
         <v>637</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>638</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>19</v>
       </c>
@@ -13178,7 +13196,7 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13199,10 +13217,10 @@
         <v>19</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>607</v>
+        <v>19</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>19</v>
@@ -13213,10 +13231,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13227,7 +13245,7 @@
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>19</v>
@@ -13236,10 +13254,10 @@
         <v>19</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>640</v>
+        <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>641</v>
@@ -13247,9 +13265,7 @@
       <c r="M90" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="N90" t="s" s="2">
-        <v>643</v>
-      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>19</v>
@@ -13298,13 +13314,13 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>19</v>
@@ -13319,10 +13335,10 @@
         <v>19</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>644</v>
+        <v>612</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>19</v>
@@ -13333,10 +13349,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13359,16 +13375,16 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13418,7 +13434,7 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13439,10 +13455,10 @@
         <v>19</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>19</v>
@@ -13453,10 +13469,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13479,7 +13495,7 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>587</v>
+        <v>652</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>653</v>
@@ -13490,9 +13506,7 @@
       <c r="N92" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="O92" t="s" s="2">
-        <v>656</v>
-      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>19</v>
       </c>
@@ -13540,7 +13554,7 @@
         <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13561,10 +13575,10 @@
         <v>19</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>19</v>
@@ -13575,10 +13589,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13589,7 +13603,7 @@
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>19</v>
@@ -13598,19 +13612,23 @@
         <v>19</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>105</v>
+        <v>592</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>106</v>
+        <v>658</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+        <v>659</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>661</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>19</v>
       </c>
@@ -13658,19 +13676,19 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>108</v>
+        <v>657</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>19</v>
@@ -13679,10 +13697,10 @@
         <v>19</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>19</v>
+        <v>662</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>109</v>
+        <v>663</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>19</v>
@@ -13693,21 +13711,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>19</v>
@@ -13719,17 +13737,15 @@
         <v>19</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>19</v>
@@ -13778,19 +13794,19 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>19</v>
@@ -13813,14 +13829,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>598</v>
+        <v>111</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13833,26 +13849,24 @@
         <v>19</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>599</v>
+        <v>113</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>600</v>
+        <v>114</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O95" t="s" s="2">
-        <v>248</v>
-      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>19</v>
       </c>
@@ -13900,7 +13914,7 @@
         <v>19</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>601</v>
+        <v>119</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13924,7 +13938,7 @@
         <v>19</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>19</v>
@@ -13935,45 +13949,45 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>19</v>
+        <v>603</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J96" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>271</v>
+        <v>112</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>663</v>
+        <v>604</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>664</v>
+        <v>605</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>665</v>
+        <v>115</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>356</v>
+        <v>253</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>19</v>
@@ -13998,13 +14012,13 @@
         <v>19</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>553</v>
+        <v>19</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>666</v>
+        <v>19</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>667</v>
+        <v>19</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>19</v>
@@ -14022,34 +14036,34 @@
         <v>19</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>662</v>
+        <v>606</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>668</v>
+        <v>19</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>361</v>
+        <v>189</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>19</v>
@@ -14057,10 +14071,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14068,7 +14082,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>91</v>
@@ -14083,19 +14097,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="L97" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>672</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>458</v>
+        <v>361</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>19</v>
@@ -14120,13 +14134,13 @@
         <v>19</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>19</v>
+        <v>558</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>19</v>
+        <v>671</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>19</v>
+        <v>672</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>19</v>
@@ -14144,10 +14158,10 @@
         <v>19</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>91</v>
@@ -14165,16 +14179,16 @@
         <v>673</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>462</v>
+        <v>365</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>463</v>
+        <v>366</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>19</v>
+        <v>367</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>464</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" hidden="true">
@@ -14202,22 +14216,22 @@
         <v>19</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>271</v>
+        <v>675</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>676</v>
+        <v>461</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>677</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>525</v>
+        <v>463</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>19</v>
@@ -14242,13 +14256,13 @@
         <v>19</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>526</v>
+        <v>19</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>527</v>
+        <v>19</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>19</v>
@@ -14275,7 +14289,7 @@
         <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>528</v>
+        <v>19</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>103</v>
@@ -14284,38 +14298,38 @@
         <v>19</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>19</v>
+        <v>678</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>189</v>
+        <v>467</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>529</v>
+        <v>468</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>19</v>
+        <v>469</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>531</v>
+        <v>19</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>19</v>
@@ -14327,19 +14341,19 @@
         <v>19</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>532</v>
+        <v>680</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>533</v>
+        <v>681</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>534</v>
+        <v>682</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>19</v>
@@ -14367,37 +14381,37 @@
         <v>149</v>
       </c>
       <c r="Y99" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="Z99" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>678</v>
-      </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>19</v>
+        <v>533</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>103</v>
@@ -14406,31 +14420,31 @@
         <v>19</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>537</v>
+        <v>19</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>538</v>
+        <v>189</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>540</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>19</v>
+        <v>536</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14449,19 +14463,19 @@
         <v>19</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>682</v>
+        <v>537</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>683</v>
+        <v>538</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>590</v>
+        <v>539</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>591</v>
+        <v>540</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>19</v>
@@ -14486,13 +14500,13 @@
         <v>19</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>19</v>
+        <v>684</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>19</v>
+        <v>685</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>19</v>
@@ -14510,7 +14524,7 @@
         <v>19</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14528,23 +14542,145 @@
         <v>19</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>19</v>
+        <v>542</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>593</v>
+        <v>543</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>594</v>
+        <v>544</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP100" t="s" s="2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP100">
+  <autoFilter ref="A1:AP101">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14554,7 +14690,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI99">
+  <conditionalFormatting sqref="A2:AI100">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-observation.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:17:39+00:00</t>
+    <t>2026-08-31T14:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -670,7 +670,7 @@
     <t>History</t>
   </si>
   <si>
-    <t>Indicates if an observation (or possibly awhole report) is 'history', i.e. a copy/repetition af information sent previously.</t>
+    <t>Indicates if an observation (or possibly a whole report) is 'history', i.e. a copy/repetition of information sent previously.</t>
   </si>
   <si>
     <t>Observation.extension:investigationdate</t>
